--- a/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
+++ b/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
@@ -7,17 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_variable_audit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_raw_codebook" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_triplet_status" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="male_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="male_contrasts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_terms" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_review" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_design_review" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reviewer_risk_summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet_index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_variable_audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_raw_codebook" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_triplet_status" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="male_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="male_contrasts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_terms" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_review" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_design_review" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reviewer_risk_summary" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,12 +40,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,9 +65,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,277 +434,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>README</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>additional_file_5_survey_design_and_sex_comparator_audits.xlsx</t>
+          <t>Workbook overview.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Source note</t>
+          <t>survey_variable_audit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Generated from aggregate project outputs produced from approved downloaded cohort files cleaned by the authors.</t>
+          <t>Cleaned-header survey-design variable audit.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Updated by</t>
+          <t>survey_raw_codebook</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>scripts/apply_phase48_claude_minor_fixes.py</t>
+          <t>Raw/codebook/dofile survey-design audit evidence.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Updated on</t>
+          <t>survey_triplet_status</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07T11:33:36.723902+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>Weight, PSU and strata triplet availability status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>male_summary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>All-sex baseline male/female summary.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Sheet name</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Present</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>male_contrasts</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>All-sex baseline domain contrasts.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>sex_interaction_summary</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Workbook index and provenance notes.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>All-sex LFO severity-by-sex interaction summary.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>survey_variable_audit</t>
+          <t>sex_interaction_terms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cleaned-file survey-design variable audit.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Interaction model terms.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>survey_raw_codebook</t>
+          <t>sex_interaction_review</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raw/codebook/dofile survey-design evidence scan.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Women-only rationale and sex-interaction review table.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>survey_triplet_status</t>
+          <t>survey_design_review</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cohort-level weight/PSU/strata triplet status and analysis decision.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Survey-design limitations and interpretation review.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>male_summary</t>
+          <t>reviewer_risk_summary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>All-sex baseline male-comparator domain summary.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>male_contrasts</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Women-versus-men baseline domain contrasts.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>sex_interaction_summary</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>All-sex LFO severity-by-sex interaction model summary.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>sex_interaction_terms</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>All-sex LFO severity-by-sex interaction model terms.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sex_interaction_review</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Phase47 reviewer-facing women-only rationale and sex-interaction summary.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>survey_design_review</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Phase47 reviewer-facing survey-design availability summary.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>reviewer_risk_summary</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Phase47 consolidated reviewer-risk guardrail summary.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Reviewer-risk response summary for unresolved guardrails.</t>
         </is>
       </c>
     </row>
@@ -707,6 +591,540 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_tier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>event_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>female_n</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>male_n</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>interaction_or</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>interaction_ci</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>interaction_p_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>nominal_interaction_p_lt_0_05</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>phase47_interpretation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>scale_note</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>women_only_implication</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strict_primary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CHARLS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11272</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27.741305890702627</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5581</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.1974378084242778</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.04 to 1.38</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0128663879498276</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>nominal cohort-specific interaction; not consistent across cohorts</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>strict_primary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ELSA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9327</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26.29998927843894</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.8694472823936408</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.74 to 1.02</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0785218774812771</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>no nominal interaction signal</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>strict_primary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15573</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>35.44596416875361</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9431</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.9756850713573748</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.87 to 1.09</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.6684226232800854</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>no nominal interaction signal</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bridge_sensitivity</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KLoSA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1564</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23.225423225423224</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.8860348939472494</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.75 to 1.05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.1678683020310386</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>no nominal interaction signal</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>strict_primary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MHAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9818</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>22.9170910572418</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4375</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.0118928508527885</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.86 to 1.19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.8850266540461746</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>no nominal interaction signal</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>strict_primary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHARE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>22246</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10.24453834397195</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12205</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10041</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.1226349242142075</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.98 to 1.29</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0993890999492825</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no nominal interaction signal</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>all-sex baseline scale; not used for women-only profile construction</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1107,7 +1525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1238,6 +1656,290 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>additional_file_5_survey_design_and_sex_comparator_audits.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source note</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Generated from aggregate project outputs produced from approved downloaded cohort files cleaned by the authors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Updated by</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>scripts/apply_phase48_claude_minor_fixes.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Updated on</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-07T11:33:36.723902+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Sheet name</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Workbook index and provenance notes.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>survey_variable_audit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cleaned-file survey-design variable audit.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>survey_raw_codebook</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Raw/codebook/dofile survey-design evidence scan.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>survey_triplet_status</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cohort-level weight/PSU/strata triplet status and analysis decision.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>male_summary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>All-sex baseline male-comparator domain summary.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>male_contrasts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Women-versus-men baseline domain contrasts.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sex_interaction_summary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>All-sex LFO severity-by-sex interaction model summary.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sex_interaction_terms</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All-sex LFO severity-by-sex interaction model terms.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sex_interaction_review</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Phase47 reviewer-facing women-only rationale and sex-interaction summary.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>survey_design_review</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Phase47 reviewer-facing survey-design availability summary.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reviewer_risk_summary</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Phase47 consolidated reviewer-risk guardrail summary.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2218,7 +2920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -67420,7 +68122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -67821,7 +68523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -68855,7 +69557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69256,7 +69958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69898,7 +70600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -71846,538 +72548,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>analysis_tier</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>events</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>event_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>female_n</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>male_n</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>interaction_or</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>interaction_ci</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>interaction_p_value</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>nominal_interaction_p_lt_0_05</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>phase47_interpretation</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>scale_note</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>women_only_implication</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>strict_primary</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CHARLS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>11272</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>27.741305890702627</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5691</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.1974378084242778</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1.04 to 1.38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.0128663879498276</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>nominal cohort-specific interaction; not consistent across cohorts</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>strict_primary</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ELSA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>9327</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>26.29998927843894</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.8694472823936408</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.74 to 1.02</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0785218774812771</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>no nominal interaction signal</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>strict_primary</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HRS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>15573</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5520</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>35.44596416875361</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9431</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6142</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.9756850713573748</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.87 to 1.09</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.6684226232800854</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>no nominal interaction signal</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bridge_sensitivity</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KLoSA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6734</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23.225423225423224</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3834</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.8860348939472494</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.75 to 1.05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.1678683020310386</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>no nominal interaction signal</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>strict_primary</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MHAS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>9818</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>22.9170910572418</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5443</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4375</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.0118928508527885</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.86 to 1.19</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.8850266540461746</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>no nominal interaction signal</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>strict_primary</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SHARE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>22246</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2279</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10.24453834397195</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>12205</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>10041</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.1226349242142075</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.98 to 1.29</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.0993890999492825</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>no nominal interaction signal</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>all-sex baseline scale; not used for women-only profile construction</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Supports focused older-women reporting only; does not establish a women-specific mechanism.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
+++ b/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
@@ -19,6 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sex_interaction_review" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey_design_review" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reviewer_risk_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase61_corrected_status" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase61_weighted_metrics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase61_weighted_terms" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase61_weighted_class_risks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase61_skipped" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,11 +439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Workbook overview.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -473,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cleaned-header survey-design variable audit.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -485,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raw/codebook/dofile survey-design audit evidence.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -497,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Weight, PSU and strata triplet availability status.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -509,7 +514,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>All-sex baseline male/female summary.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -521,7 +526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>All-sex baseline domain contrasts.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -533,7 +538,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>All-sex LFO severity-by-sex interaction summary.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -545,7 +550,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Interaction model terms.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -557,7 +562,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Women-only rationale and sex-interaction review table.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -569,7 +574,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Survey-design limitations and interpretation review.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
         </is>
       </c>
     </row>
@@ -581,7 +586,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reviewer-risk response summary for unresolved guardrails.</t>
+          <t>Workbook sheet used by the manuscript package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>phase61_corrected_status</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Corrected cleaned-file and metadata survey-design availability status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>phase61_weighted_metrics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Weight-only LFO sensitivity model metrics where cleaned weights were available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>phase61_weighted_terms</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Weight-only LFO sensitivity model coefficients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>phase61_weighted_class_risks</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Unweighted and weight-only class risks for LFO profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>phase61_skipped</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cohorts skipped from Phase61 modelling and reasons.</t>
         </is>
       </c>
     </row>
@@ -1647,6 +1712,5350 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Mortality remains secondary; hospitalization remains feasibility/sensitivity; no independent hard-outcome validation claim.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>weight_cleaned_variable_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>weight_cleaned_variables</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>weight_metadata_nonempty_mentions</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>weight_metadata_evidence</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>psu_cleaned_variable_count</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>psu_cleaned_variables</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>psu_metadata_nonempty_mentions</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>psu_metadata_evidence</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>strata_cleaned_variable_count</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>strata_cleaned_variables</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>strata_metadata_nonempty_mentions</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>strata_metadata_evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>full_cleaned_triplet_available</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>full_metadata_triplet_available</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>phase61_analysis_decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CHARLS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>188</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ELSA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>722</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>weight_only_sensitivity_modelable_no_psu_or_strata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KLoSA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LASI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MHAS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SHARE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>217</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>model_type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>weighting</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>weight_variable</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_unweighted</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_weighted</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>aic_or_pseudo_aic</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>weight_mean</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>weight_p01</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>weight_p99</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>design_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H3" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L3" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L4" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L5" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G6" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L6" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H7" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L7" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>model_type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>weighting</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>weight_variable</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_unweighted</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_weighted</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>aic_or_pseudo_aic</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>weight_mean</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>weight_p01</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>weight_p99</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>design_note</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>log_or</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>-4.103497573360236</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0165148125026219</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0112571369720698</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0242280992648001</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.946384834629071e-98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H3" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L3" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.2]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3310116082870475</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.392375955314149</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.253883165646517</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.546165427571847</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.91984415953546e-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H4" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L4" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.3]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4857292870325222</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.625359930638258</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.426346394669971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.852141186738628</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.127406073629252e-13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L5" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.4]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5182956521803153</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.679163331132381</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.40291056432927</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.009814142334608</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.590387218021547e-08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G6" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L6" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.055404346508027</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.056967909565404</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.051444489752262</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.06252034485842</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.033050606567672e-95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H7" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L7" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.1922282916839094</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8251184793015933</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7652306601094644</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8896931871333855</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.728252028701952e-07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L8" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0235963525233803</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.023876949121722</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.006626217969098</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.041423309098618</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0064936687204108</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G9" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L9" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1072034777462315</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.11316073487421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.974893128091125</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.271038625630631</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1131463653968483</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G10" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H10" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.693310502660357</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11145.08702554369</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.2844079069103525</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7524596486071095</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6838256346139595</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8279823015139954</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5.604763896937089e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G11" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L11" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>-4.232938742998879</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0145096875898179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.009942952292817799</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0211738956151073</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.485997960273625e-107</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G12" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H12" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L12" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.2]</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3310548910877856</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.392436222549433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.252572554511104</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.547917225940261</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.807760899623684e-10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H13" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L13" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.3]</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.4463267528819087</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.56256195474933</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.367055405510203</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.786028461310834</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5.970574408365835e-11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H14" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L14" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.4]</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4841358142619584</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.622772026271582</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.344519498282077</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.958609787819602</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.544210400280266e-07</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G15" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H15" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.056849703742831</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.058496710345938</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.053090181123056</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.063930996506224</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5.697033645563531e-105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G16" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L16" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.1817507137664214</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.8338091716578511</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.7719124837163592</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.900669116521528</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.869028499090716e-06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G17" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H17" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L17" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0319333317703947</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.032448671485543</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.014882326850032</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.050319067591546</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.0002651243532195</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G18" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H18" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L18" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1078303737216008</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.113858789639842</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9761698575362848</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.270968770116749</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1092205228223054</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H19" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7054309780469316</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10867.11792191051</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L19" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.3236167429394562</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7235274862662193</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.657254291341085</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7964832337793679</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.04531044559461e-11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G20" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H20" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L20" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>-4.241403255801109</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0143873884848335</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0098538229789205</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.0210067653799274</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6.443267105041924e-107</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G21" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H21" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L21" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.2]</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.331336098986538</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.392827841674338</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.252904659583981</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.548377509576308</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.574263483901137e-10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G22" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H22" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L22" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.3]</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4465475730523781</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.56290703804582</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.367488469040737</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.786251558879063</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5.661501578073907e-11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G23" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H23" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L23" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>C(lfo_profile_class, Treatment(reference=1))[T.4]</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.4867602668434651</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.627036508022473</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.348278036980981</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.963428703745402</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.844969765728521e-07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G24" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H24" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L24" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0569863830274716</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.058641394806561</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.053229081658769</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.064081520644033</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.838307339490361e-105</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G25" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H25" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L25" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1813361795616343</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8341548857299719</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7722233131920145</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9010533112643376</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.084215785427512e-06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G26" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H26" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L26" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0313960971793385</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.03189415331224</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.014340128314962</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.049751965752214</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.000335242461664</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G27" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H27" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L27" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1078422629350608</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.11387203262348</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.97613346064852</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.271046383592326</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.1093135115215293</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>lfo_profile</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H28" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.705551752420112</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10869.22139794893</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L28" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.3251359250546248</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.7224291507463286</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.656256839683359</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.795273810936398</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.279698622590894e-11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G29" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H29" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L29" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>-3.891055281117968</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.0204237818304651</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0138469532142183</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0301243788294252</v>
+      </c>
+      <c r="T29" t="n">
+        <v>9.763833031653026e-86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G30" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H30" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J30" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L30" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0532197628600005</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.054661395057919</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.048931150069638</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.060422944014647</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.044832360400288e-81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G31" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H31" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L31" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.0848695508350564</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.9186321113774424</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.8473018953970454</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.9959672705067344</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.0395950452248882</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G32" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H32" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J32" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L32" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0152801354031518</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.015397473557967</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9981115674925508</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.03298274750793</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.0811243742829269</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G33" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H33" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L33" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.08784060934888049</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.091814083200862</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.9555930501009148</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.247453601875665</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.1963891849557478</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G34" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H34" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J34" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L34" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.2360708992861138</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.7897246810317863</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.7170184225053744</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.8698034140483774</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.662774854731589e-06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G35" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H35" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L35" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>cognitive_score</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.1348307812226016</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.144343123621957</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.084298819951831</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.207712450188807</v>
+      </c>
+      <c r="T35" t="n">
+        <v>9.433718787309112e-07</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G36" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H36" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L36" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>affective_score</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.1432379600901722</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.154004375981218</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.100789255754441</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.209792058581717</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.738014874397217e-09</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G37" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H37" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7014262773259663</v>
+      </c>
+      <c r="J37" t="n">
+        <v>11083.57739106666</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L37" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>cardiometabolic_chronic_score</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.1683587655013795</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.183361083632609</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.127559798270373</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.241923892998142</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8.408475602929911e-12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G38" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L38" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>-4.062255248666856</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.017210162120544</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.0116972557950681</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0253212963283483</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.860009906608852e-94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G39" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H39" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L39" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.055335683136645</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.056895337076855</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.051269919256932</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.062550856895388</v>
+      </c>
+      <c r="T39" t="n">
+        <v>8.171015488584607e-92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G40" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H40" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L40" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.0804826304119455</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.9226709298585328</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.8500050683134338</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.001548904284992</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.0544820093532651</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G41" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H41" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L41" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M41" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0234549740167059</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.02373220515972</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.006125706865867</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.04164680489662</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.008050785645673001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G42" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H42" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J42" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L42" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.0862184083891244</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.090044377144737</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9547855767868112</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.244464488187554</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.2021378360415688</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G43" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H43" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J43" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L43" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>-0.2743994206156949</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.7600284435976584</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6897347996715667</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.8374859951281816</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.995792373496537e-08</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G44" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H44" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J44" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L44" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>cognitive_score</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.1269870751857051</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.13540234282222</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.07457402125244</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.199673968093576</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6.180538476767078e-06</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G45" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H45" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J45" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L45" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M45" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>affective_score</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.1517389434915643</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.16385636449113</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.109221751488165</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.221182000216989</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6.188817802308165e-10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>weight_only_norm</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G46" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H46" t="n">
+        <v>36.54211323323907</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.712800681007329</v>
+      </c>
+      <c r="J46" t="n">
+        <v>10806.28634817143</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L46" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>cardiometabolic_chronic_score</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.1613096515147552</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.175048768116421</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.118137529950902</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.23485668843666</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.910059958170992e-10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G47" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H47" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J47" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L47" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>-4.066667423526982</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.0171343951473789</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.0116401499996287</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.0252219685378526</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.99232566852508e-94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G48" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H48" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L48" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M48" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.0554139074327197</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.056978015204299</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.051346347670684</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.062639849465824</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6.987725590639449e-92</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G49" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H49" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J49" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L49" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>cov_education_raw</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>-0.07991635755858489</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.9231935613207356</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.8504831616335164</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.002120194863215</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.0562154214851964</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G50" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H50" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L50" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>cov_marital_status_raw</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.0229701049255135</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.023235949375048</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.00564160984259</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.04113811306728</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.0094400810665071</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G51" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H51" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J51" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L51" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>cov_smoking_raw</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0862657139138512</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.09009594348565</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9547847232149144</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.244583346497879</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.2020544721178502</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G52" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H52" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J52" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L52" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M52" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>cov_drinking_raw</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>-0.2760478765997899</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.7587766022478897</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.6886046147317798</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.8360994390708678</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.46870462797679e-08</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G53" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H53" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J53" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L53" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M53" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>cognitive_score</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0.1279727545320955</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.13652203720054</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.075641576299907</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.20084828394763</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5.218502122923911e-06</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G54" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H54" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J54" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L54" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M54" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>affective_score</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.1508635454471038</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.162837972719738</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.108213662395883</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.220154737919043</v>
+      </c>
+      <c r="T54" t="n">
+        <v>7.969457631113891e-10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>continuous_three_domain</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>weight_only_trim99</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>9081</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G55" t="n">
+        <v>38.29974672392908</v>
+      </c>
+      <c r="H55" t="n">
+        <v>36.57710864162173</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7128842913654345</v>
+      </c>
+      <c r="J55" t="n">
+        <v>10808.46093340265</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3467.113093271666</v>
+      </c>
+      <c r="L55" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="M55" t="n">
+        <v>10567.20000000051</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>weight-only normalized GLM; no cleaned PSU/strata available in current model frame</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>cardiometabolic_chronic_score</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.1617170378703512</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.175527564472641</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.118627783364182</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1.235321592566861</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.675510147336579e-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="51" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>lfo_profile_class</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_unweighted</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_weighted_norm</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>event_pct_weighted_trim99</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>weight_variable</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>design_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3614</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.3027116768124</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.59148309847673</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.61382159220768</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>weight-only descriptive class risk; no PSU/strata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3280</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E3" t="n">
+        <v>40.67073170731707</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39.71054145099006</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.73935644018224</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>weight-only descriptive class risk; no PSU/strata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1541</v>
+      </c>
+      <c r="D4" t="n">
+        <v>751</v>
+      </c>
+      <c r="E4" t="n">
+        <v>48.73458792991564</v>
+      </c>
+      <c r="F4" t="n">
+        <v>47.52941730459476</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47.52357258021189</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>weight-only descriptive class risk; no PSU/strata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>646</v>
+      </c>
+      <c r="D5" t="n">
+        <v>334</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51.70278637770897</v>
+      </c>
+      <c r="F5" t="n">
+        <v>51.34927027177289</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51.41511785122839</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>wtresp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>weight-only descriptive class risk; no PSU/strata</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>phase61_analysis_decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CHARLS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ELSA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KLoSA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LASI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MHAS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>not_modelable_from_current_cleaned_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHARE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no cleaned weight variable available for model frame</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>metadata_mentions_only_no_cleaned_design_variables</t>
         </is>
       </c>
     </row>

--- a/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
+++ b/manuscript_submission_snapshot/additional_files/additional_file_5_survey_design_and_sex_comparator_audits.xlsx
@@ -1838,6 +1838,7 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>188</v>
       </c>
@@ -1847,6 +1848,7 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>32</v>
       </c>
@@ -1856,6 +1858,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
@@ -1883,6 +1886,7 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>178</v>
       </c>
@@ -1892,6 +1896,7 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -1901,6 +1906,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>13</v>
       </c>
@@ -1942,6 +1948,7 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -1951,6 +1958,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>32</v>
       </c>
@@ -1978,6 +1986,7 @@
       <c r="B5" t="n">
         <v>0</v>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>40</v>
       </c>
@@ -1987,6 +1996,7 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -1996,6 +2006,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>4</v>
       </c>
@@ -2023,6 +2034,7 @@
       <c r="B6" t="n">
         <v>0</v>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>99</v>
       </c>
@@ -2032,6 +2044,7 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>7</v>
       </c>
@@ -2041,6 +2054,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>19</v>
       </c>
@@ -2068,6 +2082,7 @@
       <c r="B7" t="n">
         <v>0</v>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>95</v>
       </c>
@@ -2077,6 +2092,7 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -2086,6 +2102,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -2113,6 +2130,7 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>217</v>
       </c>
@@ -2122,6 +2140,7 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>59</v>
       </c>
@@ -2131,6 +2150,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>36</v>
       </c>
@@ -2604,10 +2624,10 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="51" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -2775,16 +2795,16 @@
         <v>-4.103497573360236</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0165148125026219</v>
+        <v>0.01651481250262199</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0112571369720698</v>
+        <v>0.01125713697206985</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0242280992648001</v>
+        <v>0.02422809926480011</v>
       </c>
       <c r="T2" t="n">
-        <v>8.946384834629071e-98</v>
+        <v>8.946384834629069e-98</v>
       </c>
     </row>
     <row r="3">
@@ -2855,7 +2875,7 @@
         <v>1.253883165646517</v>
       </c>
       <c r="S3" t="n">
-        <v>1.546165427571847</v>
+        <v>1.546165427571848</v>
       </c>
       <c r="T3" t="n">
         <v>5.91984415953546e-10</v>
@@ -2929,7 +2949,7 @@
         <v>1.426346394669971</v>
       </c>
       <c r="S4" t="n">
-        <v>1.852141186738628</v>
+        <v>1.852141186738627</v>
       </c>
       <c r="T4" t="n">
         <v>3.127406073629252e-13</v>
@@ -3000,7 +3020,7 @@
         <v>1.679163331132381</v>
       </c>
       <c r="R5" t="n">
-        <v>1.40291056432927</v>
+        <v>1.402910564329271</v>
       </c>
       <c r="S5" t="n">
         <v>2.009814142334608</v>
@@ -3068,7 +3088,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.055404346508027</v>
+        <v>0.05540434650802703</v>
       </c>
       <c r="Q6" t="n">
         <v>1.056967909565404</v>
@@ -3142,7 +3162,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-0.1922282916839094</v>
+        <v>-0.1922282916839095</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8251184793015933</v>
@@ -3216,7 +3236,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.0235963525233803</v>
+        <v>0.02359635252338034</v>
       </c>
       <c r="Q8" t="n">
         <v>1.023876949121722</v>
@@ -3228,7 +3248,7 @@
         <v>1.041423309098618</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0064936687204108</v>
+        <v>0.006493668720410871</v>
       </c>
     </row>
     <row r="9">
@@ -3290,7 +3310,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.1072034777462315</v>
+        <v>0.1072034777462316</v>
       </c>
       <c r="Q9" t="n">
         <v>1.11316073487421</v>
@@ -3364,7 +3384,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-0.2844079069103525</v>
+        <v>-0.2844079069103526</v>
       </c>
       <c r="Q10" t="n">
         <v>0.7524596486071095</v>
@@ -3441,13 +3461,13 @@
         <v>-4.232938742998879</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0145096875898179</v>
+        <v>0.01450968758981796</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009942952292817799</v>
+        <v>0.009942952292817841</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0211738956151073</v>
+        <v>0.02117389561510736</v>
       </c>
       <c r="T11" t="n">
         <v>8.485997960273625e-107</v>
@@ -3524,7 +3544,7 @@
         <v>1.547917225940261</v>
       </c>
       <c r="T12" t="n">
-        <v>8.807760899623684e-10</v>
+        <v>8.807760899623685e-10</v>
       </c>
     </row>
     <row r="13">
@@ -3586,7 +3606,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.4463267528819087</v>
+        <v>0.4463267528819088</v>
       </c>
       <c r="Q13" t="n">
         <v>1.56256195474933</v>
@@ -3595,10 +3615,10 @@
         <v>1.367055405510203</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786028461310834</v>
+        <v>1.786028461310833</v>
       </c>
       <c r="T13" t="n">
-        <v>5.970574408365835e-11</v>
+        <v>5.970574408365836e-11</v>
       </c>
     </row>
     <row r="14">
@@ -3734,7 +3754,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.056849703742831</v>
+        <v>0.05684970374283101</v>
       </c>
       <c r="Q15" t="n">
         <v>1.058496710345938</v>
@@ -3808,7 +3828,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-0.1817507137664214</v>
+        <v>-0.1817507137664215</v>
       </c>
       <c r="Q16" t="n">
         <v>0.8338091716578511</v>
@@ -3882,7 +3902,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.0319333317703947</v>
+        <v>0.03193333177039473</v>
       </c>
       <c r="Q17" t="n">
         <v>1.032448671485543</v>
@@ -3891,10 +3911,10 @@
         <v>1.014882326850032</v>
       </c>
       <c r="S17" t="n">
-        <v>1.050319067591546</v>
+        <v>1.050319067591545</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0002651243532195</v>
+        <v>0.0002651243532195516</v>
       </c>
     </row>
     <row r="18">
@@ -3956,13 +3976,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.1078303737216008</v>
+        <v>0.1078303737216009</v>
       </c>
       <c r="Q18" t="n">
         <v>1.113858789639842</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9761698575362848</v>
+        <v>0.9761698575362847</v>
       </c>
       <c r="S18" t="n">
         <v>1.270968770116749</v>
@@ -4107,13 +4127,13 @@
         <v>-4.241403255801109</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0143873884848335</v>
+        <v>0.01438738848483359</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0098538229789205</v>
+        <v>0.009853822978920549</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0210067653799274</v>
+        <v>0.02100676537992749</v>
       </c>
       <c r="T20" t="n">
         <v>6.443267105041924e-107</v>
@@ -4187,7 +4207,7 @@
         <v>1.252904659583981</v>
       </c>
       <c r="S21" t="n">
-        <v>1.548377509576308</v>
+        <v>1.548377509576307</v>
       </c>
       <c r="T21" t="n">
         <v>8.574263483901137e-10</v>
@@ -4409,7 +4429,7 @@
         <v>1.053229081658769</v>
       </c>
       <c r="S24" t="n">
-        <v>1.064081520644033</v>
+        <v>1.064081520644034</v>
       </c>
       <c r="T24" t="n">
         <v>2.838307339490361e-105</v>
@@ -4483,7 +4503,7 @@
         <v>0.7722233131920145</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9010533112643376</v>
+        <v>0.9010533112643377</v>
       </c>
       <c r="T25" t="n">
         <v>4.084215785427512e-06</v>
@@ -4548,7 +4568,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.0313960971793385</v>
+        <v>0.03139609717933859</v>
       </c>
       <c r="Q26" t="n">
         <v>1.03189415331224</v>
@@ -4557,10 +4577,10 @@
         <v>1.014340128314962</v>
       </c>
       <c r="S26" t="n">
-        <v>1.049751965752214</v>
+        <v>1.049751965752215</v>
       </c>
       <c r="T26" t="n">
-        <v>0.000335242461664</v>
+        <v>0.0003352424616640282</v>
       </c>
     </row>
     <row r="27">
@@ -4622,13 +4642,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.1078422629350608</v>
+        <v>0.1078422629350609</v>
       </c>
       <c r="Q27" t="n">
         <v>1.11387203262348</v>
       </c>
       <c r="R27" t="n">
-        <v>0.97613346064852</v>
+        <v>0.9761334606485199</v>
       </c>
       <c r="S27" t="n">
         <v>1.271046383592326</v>
@@ -4773,13 +4793,13 @@
         <v>-3.891055281117968</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0204237818304651</v>
+        <v>0.02042378183046517</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0138469532142183</v>
+        <v>0.01384695321421831</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0301243788294252</v>
+        <v>0.03012437882942521</v>
       </c>
       <c r="T29" t="n">
         <v>9.763833031653026e-86</v>
@@ -4844,7 +4864,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.0532197628600005</v>
+        <v>0.05321976286000053</v>
       </c>
       <c r="Q30" t="n">
         <v>1.054661395057919</v>
@@ -4918,10 +4938,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-0.0848695508350564</v>
+        <v>-0.08486955083505648</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9186321113774424</v>
+        <v>0.9186321113774425</v>
       </c>
       <c r="R31" t="n">
         <v>0.8473018953970454</v>
@@ -4930,7 +4950,7 @@
         <v>0.9959672705067344</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0395950452248882</v>
+        <v>0.03959504522488828</v>
       </c>
     </row>
     <row r="32">
@@ -4992,7 +5012,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.0152801354031518</v>
+        <v>0.01528013540315184</v>
       </c>
       <c r="Q32" t="n">
         <v>1.015397473557967</v>
@@ -5004,7 +5024,7 @@
         <v>1.03298274750793</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0811243742829269</v>
+        <v>0.08112437428292693</v>
       </c>
     </row>
     <row r="33">
@@ -5066,19 +5086,19 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.08784060934888049</v>
+        <v>0.08784060934888052</v>
       </c>
       <c r="Q33" t="n">
         <v>1.091814083200862</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9555930501009148</v>
+        <v>0.9555930501009147</v>
       </c>
       <c r="S33" t="n">
         <v>1.247453601875665</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1963891849557478</v>
+        <v>0.1963891849557479</v>
       </c>
     </row>
     <row r="34">
@@ -5214,7 +5234,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.1348307812226016</v>
+        <v>0.1348307812226017</v>
       </c>
       <c r="Q35" t="n">
         <v>1.144343123621957</v>
@@ -5226,7 +5246,7 @@
         <v>1.207712450188807</v>
       </c>
       <c r="T35" t="n">
-        <v>9.433718787309112e-07</v>
+        <v>9.433718787309111e-07</v>
       </c>
     </row>
     <row r="36">
@@ -5288,7 +5308,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.1432379600901722</v>
+        <v>0.1432379600901723</v>
       </c>
       <c r="Q36" t="n">
         <v>1.154004375981218</v>
@@ -5439,16 +5459,16 @@
         <v>-4.062255248666856</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.017210162120544</v>
+        <v>0.01721016212054405</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0116972557950681</v>
+        <v>0.01169725579506811</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0253212963283483</v>
+        <v>0.02532129632834831</v>
       </c>
       <c r="T38" t="n">
-        <v>1.860009906608852e-94</v>
+        <v>1.860009906608851e-94</v>
       </c>
     </row>
     <row r="39">
@@ -5510,7 +5530,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.055335683136645</v>
+        <v>0.05533568313664506</v>
       </c>
       <c r="Q39" t="n">
         <v>1.056895337076855</v>
@@ -5584,10 +5604,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>-0.0804826304119455</v>
+        <v>-0.08048263041194556</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9226709298585328</v>
+        <v>0.9226709298585327</v>
       </c>
       <c r="R40" t="n">
         <v>0.8500050683134338</v>
@@ -5596,7 +5616,7 @@
         <v>1.001548904284992</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0544820093532651</v>
+        <v>0.05448200935326513</v>
       </c>
     </row>
     <row r="41">
@@ -5658,7 +5678,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.0234549740167059</v>
+        <v>0.02345497401670594</v>
       </c>
       <c r="Q41" t="n">
         <v>1.02373220515972</v>
@@ -5670,7 +5690,7 @@
         <v>1.04164680489662</v>
       </c>
       <c r="T41" t="n">
-        <v>0.008050785645673001</v>
+        <v>0.008050785645673013</v>
       </c>
     </row>
     <row r="42">
@@ -5732,19 +5752,19 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.0862184083891244</v>
+        <v>0.08621840838912444</v>
       </c>
       <c r="Q42" t="n">
         <v>1.090044377144737</v>
       </c>
       <c r="R42" t="n">
-        <v>0.9547855767868112</v>
+        <v>0.9547855767868111</v>
       </c>
       <c r="S42" t="n">
         <v>1.244464488187554</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2021378360415688</v>
+        <v>0.2021378360415689</v>
       </c>
     </row>
     <row r="43">
@@ -5954,7 +5974,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.1517389434915643</v>
+        <v>0.1517389434915644</v>
       </c>
       <c r="Q45" t="n">
         <v>1.16385636449113</v>
@@ -6105,13 +6125,13 @@
         <v>-4.066667423526982</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0171343951473789</v>
+        <v>0.01713439514737894</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0116401499996287</v>
+        <v>0.0116401499996288</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0252219685378526</v>
+        <v>0.02522196853785262</v>
       </c>
       <c r="T47" t="n">
         <v>1.99232566852508e-94</v>
@@ -6176,7 +6196,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.0554139074327197</v>
+        <v>0.05541390743271971</v>
       </c>
       <c r="Q48" t="n">
         <v>1.056978015204299</v>
@@ -6188,7 +6208,7 @@
         <v>1.062639849465824</v>
       </c>
       <c r="T48" t="n">
-        <v>6.987725590639449e-92</v>
+        <v>6.98772559063945e-92</v>
       </c>
     </row>
     <row r="49">
@@ -6250,10 +6270,10 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>-0.07991635755858489</v>
+        <v>-0.07991635755858495</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9231935613207356</v>
+        <v>0.9231935613207355</v>
       </c>
       <c r="R49" t="n">
         <v>0.8504831616335164</v>
@@ -6262,7 +6282,7 @@
         <v>1.002120194863215</v>
       </c>
       <c r="T49" t="n">
-        <v>0.0562154214851964</v>
+        <v>0.05621542148519645</v>
       </c>
     </row>
     <row r="50">
@@ -6324,7 +6344,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.0229701049255135</v>
+        <v>0.02297010492551357</v>
       </c>
       <c r="Q50" t="n">
         <v>1.023235949375048</v>
@@ -6336,7 +6356,7 @@
         <v>1.04113811306728</v>
       </c>
       <c r="T50" t="n">
-        <v>0.0094400810665071</v>
+        <v>0.009440081066507166</v>
       </c>
     </row>
     <row r="51">
@@ -6398,13 +6418,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.0862657139138512</v>
+        <v>0.08626571391385128</v>
       </c>
       <c r="Q51" t="n">
         <v>1.09009594348565</v>
       </c>
       <c r="R51" t="n">
-        <v>0.9547847232149144</v>
+        <v>0.9547847232149145</v>
       </c>
       <c r="S51" t="n">
         <v>1.244583346497879</v>
@@ -6472,7 +6492,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>-0.2760478765997899</v>
+        <v>-0.27604787659979</v>
       </c>
       <c r="Q52" t="n">
         <v>0.7587766022478897</v>
@@ -6546,7 +6566,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.1279727545320955</v>
+        <v>0.1279727545320956</v>
       </c>
       <c r="Q53" t="n">
         <v>1.13652203720054</v>
@@ -6558,7 +6578,7 @@
         <v>1.20084828394763</v>
       </c>
       <c r="T53" t="n">
-        <v>5.218502122923911e-06</v>
+        <v>5.21850212292391e-06</v>
       </c>
     </row>
     <row r="54">
@@ -6620,7 +6640,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.1508635454471038</v>
+        <v>0.1508635454471039</v>
       </c>
       <c r="Q54" t="n">
         <v>1.162837972719738</v>
@@ -6873,7 +6893,7 @@
         <v>47.52941730459476</v>
       </c>
       <c r="G4" t="n">
-        <v>47.52357258021189</v>
+        <v>47.52357258021188</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
